--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N27_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0001T0006Z000C1N27_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>27.6791001965682</v>
+        <v>4.497853781942333</v>
       </c>
       <c r="D2" t="n">
-        <v>27.16544918319588</v>
+        <v>4.414385492269331</v>
       </c>
       <c r="E2" t="n">
-        <v>7.464209073951881</v>
+        <v>1.212933974517181</v>
       </c>
       <c r="F2" t="n">
-        <v>19.92693580657116</v>
+        <v>3.238127068567813</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>14.93325660762089</v>
+        <v>2.426654198738394</v>
       </c>
       <c r="D3" t="n">
-        <v>16.28939364660885</v>
+        <v>2.647026467573939</v>
       </c>
       <c r="E3" t="n">
-        <v>7.464209073951881</v>
+        <v>1.212933974517181</v>
       </c>
       <c r="F3" t="n">
-        <v>19.92693580657116</v>
+        <v>3.238127068567813</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>12.09856773816015</v>
+        <v>1.966017257451024</v>
       </c>
       <c r="D4" t="n">
-        <v>10.65140225817891</v>
+        <v>1.730852866954072</v>
       </c>
       <c r="E4" t="n">
-        <v>7.464209073951881</v>
+        <v>1.212933974517181</v>
       </c>
       <c r="F4" t="n">
-        <v>19.92693580657116</v>
+        <v>3.238127068567813</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>25.43082363177039</v>
+        <v>4.132508840162688</v>
       </c>
       <c r="D5" t="n">
-        <v>24.11748302268479</v>
+        <v>3.919090991186279</v>
       </c>
       <c r="E5" t="n">
-        <v>7.464209073951881</v>
+        <v>1.212933974517181</v>
       </c>
       <c r="F5" t="n">
-        <v>19.92693580657116</v>
+        <v>3.238127068567813</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>31.89840387863759</v>
+        <v>5.18349063027861</v>
       </c>
       <c r="D6" t="n">
-        <v>53.59453309722232</v>
+        <v>8.709111628298627</v>
       </c>
       <c r="E6" t="n">
-        <v>7.464209073951881</v>
+        <v>1.212933974517181</v>
       </c>
       <c r="F6" t="n">
-        <v>19.92693580657116</v>
+        <v>3.238127068567813</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>29.76797017839147</v>
+        <v>4.837295153988614</v>
       </c>
       <c r="D7" t="n">
-        <v>65.66131799494813</v>
+        <v>10.66996417417907</v>
       </c>
       <c r="E7" t="n">
-        <v>7.464209073951881</v>
+        <v>1.212933974517181</v>
       </c>
       <c r="F7" t="n">
-        <v>19.92693580657116</v>
+        <v>3.238127068567813</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
